--- a/sources/paul_step4.xlsx
+++ b/sources/paul_step4.xlsx
@@ -780,6 +780,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1bddff50-c0df-40c7-9efa-29b264583940</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>1bddff50-c0df-40c7-9efa-29b264583940</t>
@@ -812,6 +817,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>39dff7b9-ce44-4948-ad1f-b1ef695ca9a3</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>39dff7b9-ce44-4948-ad1f-b1ef695ca9a3</t>
@@ -849,6 +859,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>701e73a5-cb4f-442c-95a1-4a3d33f87d73</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>701e73a5-cb4f-442c-95a1-4a3d33f87d73</t>
@@ -886,6 +901,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0837c7ed-0764-4f99-a630-8ac829f5cd48</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>0837c7ed-0764-4f99-a630-8ac829f5cd48</t>
@@ -923,6 +943,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>8f4adaf4-8d96-4db4-9e5d-c30c5a7019be</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>8f4adaf4-8d96-4db4-9e5d-c30c5a7019be</t>
@@ -960,6 +985,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>9ceaa1aa-aa76-418f-a422-c4dcb6b6e146</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>9ceaa1aa-aa76-418f-a422-c4dcb6b6e146</t>
@@ -997,6 +1027,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>b7497a64-e28b-4906-90d2-9ce8f800b5db</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>b7497a64-e28b-4906-90d2-9ce8f800b5db</t>
@@ -1044,6 +1079,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>298a11b7-cb2d-4207-89d4-785146ac1d79</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>298a11b7-cb2d-4207-89d4-785146ac1d79</t>
@@ -1086,6 +1126,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>f4807f21-048f-4fcc-be89-b4ed5bad669d</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>f4807f21-048f-4fcc-be89-b4ed5bad669d</t>
@@ -1126,6 +1171,11 @@
       <c r="L17" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>714cac8f-98de-4f0c-bfac-510c28ebaccd</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -4754,6 +4804,11 @@
           <t>hhmmlmhmLm</t>
         </is>
       </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>8b2ab344-e968-4445-b403-e548e2f0db2d</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>8b2ab344-e968-4445-b403-e548e2f0db2d</t>
@@ -4781,6 +4836,11 @@
           <t>hhmhmhhlmm</t>
         </is>
       </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>9c058e2e-80b5-4da3-b171-a802077dec24</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>9c058e2e-80b5-4da3-b171-a802077dec24</t>
@@ -4806,6 +4866,11 @@
       <c r="J94" t="inlineStr">
         <is>
           <t>hhmmm</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>e1a2f47f-32a9-46a1-bc65-d50cded77733</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">

--- a/sources/paul_step4.xlsx
+++ b/sources/paul_step4.xlsx
@@ -802,6 +802,11 @@
           <t>– 1,2,1,2,1</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1,2,1,1,2</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>– Ultimate Punches</t>
@@ -842,6 +847,11 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>– 2,1,2,1,2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2,1,2,2,1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4181,6 +4191,11 @@
       <c r="A78" t="inlineStr">
         <is>
           <t>– &lt;d+4</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>&lt;d/b+4</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
